--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.02419</v>
+        <v>17.19866</v>
       </c>
       <c r="D2" t="n">
-        <v>16.75929</v>
+        <v>16.80781</v>
       </c>
       <c r="E2" t="n">
-        <v>16.95661</v>
+        <v>16.88756</v>
       </c>
       <c r="F2" t="n">
-        <v>42.71784</v>
+        <v>42.41919</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05054</v>
+        <v>0.05092</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84307</v>
+        <v>1.83921</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.7479</v>
+        <v>17.19114</v>
       </c>
       <c r="D3" t="n">
-        <v>16.76567</v>
+        <v>16.48068</v>
       </c>
       <c r="E3" t="n">
-        <v>16.87589</v>
+        <v>16.85295</v>
       </c>
       <c r="F3" t="n">
-        <v>43.02378</v>
+        <v>43.33395</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05086</v>
+        <v>0.05262</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83902</v>
+        <v>1.82884</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.28706</v>
+        <v>17.34167</v>
       </c>
       <c r="D4" t="n">
-        <v>16.69747</v>
+        <v>16.71206</v>
       </c>
       <c r="E4" t="n">
-        <v>17.16002</v>
+        <v>17.00765</v>
       </c>
       <c r="F4" t="n">
-        <v>42.97712</v>
+        <v>43.63353</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05238</v>
+        <v>0.05092</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82567</v>
+        <v>1.85464</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.92277</v>
+        <v>17.2297</v>
       </c>
       <c r="D6" t="n">
-        <v>16.3104</v>
+        <v>16.03864</v>
       </c>
       <c r="E6" t="n">
-        <v>16.31683</v>
+        <v>16.77193</v>
       </c>
       <c r="F6" t="n">
-        <v>22.17565</v>
+        <v>21.92685</v>
       </c>
       <c r="G6" t="n">
-        <v>34.74819</v>
+        <v>35.18444</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.81451</v>
+        <v>17.26659</v>
       </c>
       <c r="D7" t="n">
-        <v>16.00995</v>
+        <v>16.59833</v>
       </c>
       <c r="E7" t="n">
-        <v>16.69478</v>
+        <v>16.81295</v>
       </c>
       <c r="F7" t="n">
-        <v>22.05555</v>
+        <v>22.20196</v>
       </c>
       <c r="G7" t="n">
-        <v>34.55922</v>
+        <v>34.6768</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.87353</v>
+        <v>16.53107</v>
       </c>
       <c r="D8" t="n">
-        <v>16.25057</v>
+        <v>16.4111</v>
       </c>
       <c r="E8" t="n">
-        <v>16.81443</v>
+        <v>16.51786</v>
       </c>
       <c r="F8" t="n">
-        <v>22.29987</v>
+        <v>22.25184</v>
       </c>
       <c r="G8" t="n">
-        <v>35.24298</v>
+        <v>34.77569</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6144500000000001</v>
+        <v>0.6218900000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14075</v>
+        <v>1.13731</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61808</v>
+        <v>0.6181</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11828</v>
+        <v>1.13714</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.62358</v>
+        <v>0.61648</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09359</v>
+        <v>1.12502</v>
       </c>
     </row>
   </sheetData>
